--- a/LISTAS/ma/BISAGRAS FICHAS HERRERO DISMAY.xlsx
+++ b/LISTAS/ma/BISAGRAS FICHAS HERRERO DISMAY.xlsx
@@ -958,14 +958,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="23" t="n">
-        <v>45163.60828490167</v>
+        <v>45237</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -1011,26 +1007,6 @@
       </c>
       <c r="E11" s="7" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
     <row r="32" ht="18" customHeight="1" s="1">
       <c r="A32" s="11" t="inlineStr">
         <is>
@@ -1062,7 +1038,7 @@
       </c>
       <c r="C33" s="29" t="n"/>
       <c r="D33" s="30" t="n">
-        <v>198.436</v>
+        <v>229.273</v>
       </c>
       <c r="E33" s="31" t="n"/>
       <c r="F33" s="31" t="n"/>
@@ -1081,7 +1057,7 @@
       </c>
       <c r="C34" s="29" t="n"/>
       <c r="D34" s="30" t="n">
-        <v>217.041</v>
+        <v>300</v>
       </c>
       <c r="E34" s="31" t="n"/>
       <c r="F34" s="31" t="n"/>
@@ -1100,7 +1076,7 @@
       </c>
       <c r="C35" s="29" t="n"/>
       <c r="D35" s="30" t="n">
-        <v>242.777</v>
+        <v>280.505</v>
       </c>
       <c r="E35" s="31" t="n"/>
       <c r="F35" s="31" t="n"/>
@@ -1119,7 +1095,7 @@
       </c>
       <c r="C36" s="27" t="n"/>
       <c r="D36" s="30" t="n">
-        <v>296.106</v>
+        <v>342.12</v>
       </c>
       <c r="E36" s="31" t="n"/>
       <c r="F36" s="31" t="n"/>
@@ -1131,7 +1107,6 @@
       <c r="C37" s="14" t="n"/>
       <c r="D37" s="14" t="n"/>
     </row>
-    <row r="38"/>
     <row r="39" ht="19.5" customHeight="1" s="1">
       <c r="A39" s="13" t="inlineStr">
         <is>
@@ -1139,15 +1114,12 @@
         </is>
       </c>
     </row>
-    <row r="40"/>
     <row r="41">
       <c r="A41" s="9" t="n"/>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="A43" s="10" t="n"/>
     </row>
-    <row r="44"/>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
@@ -1157,15 +1129,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A1:D1"/>
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="B34:C34"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A1:D1"/>
     <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B36:C36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/BISAGRAS FICHAS HERRERO DISMAY.xlsx
+++ b/LISTAS/ma/BISAGRAS FICHAS HERRERO DISMAY.xlsx
@@ -958,7 +958,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="23" t="n">
-        <v>45237</v>
+        <v>45238</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
@@ -1129,15 +1129,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A1:D1"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B36:C36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/BISAGRAS FICHAS HERRERO DISMAY.xlsx
+++ b/LISTAS/ma/BISAGRAS FICHAS HERRERO DISMAY.xlsx
@@ -958,7 +958,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="23" t="n">
-        <v>45238</v>
+        <v>45239</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>

--- a/LISTAS/ma/BISAGRAS FICHAS HERRERO DISMAY.xlsx
+++ b/LISTAS/ma/BISAGRAS FICHAS HERRERO DISMAY.xlsx
@@ -1129,15 +1129,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B34:C34"/>
     <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
     <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B35:C35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/BISAGRAS FICHAS HERRERO DISMAY.xlsx
+++ b/LISTAS/ma/BISAGRAS FICHAS HERRERO DISMAY.xlsx
@@ -958,7 +958,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="23" t="n">
-        <v>45239</v>
+        <v>45253</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
@@ -1129,15 +1129,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A1:D1"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B36:C36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/BISAGRAS FICHAS HERRERO DISMAY.xlsx
+++ b/LISTAS/ma/BISAGRAS FICHAS HERRERO DISMAY.xlsx
@@ -958,7 +958,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="23" t="n">
-        <v>45253</v>
+        <v>45256</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>

--- a/LISTAS/ma/BISAGRAS FICHAS HERRERO DISMAY.xlsx
+++ b/LISTAS/ma/BISAGRAS FICHAS HERRERO DISMAY.xlsx
@@ -958,7 +958,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="23" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>

--- a/LISTAS/ma/BISAGRAS FICHAS HERRERO DISMAY.xlsx
+++ b/LISTAS/ma/BISAGRAS FICHAS HERRERO DISMAY.xlsx
@@ -958,10 +958,14 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="23" t="n">
-        <v>45266</v>
+        <v>45233.58662822087</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -1007,6 +1011,26 @@
       </c>
       <c r="E11" s="7" t="n"/>
     </row>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
     <row r="32" ht="18" customHeight="1" s="1">
       <c r="A32" s="11" t="inlineStr">
         <is>
@@ -1038,7 +1062,7 @@
       </c>
       <c r="C33" s="29" t="n"/>
       <c r="D33" s="30" t="n">
-        <v>229.273</v>
+        <v>256</v>
       </c>
       <c r="E33" s="31" t="n"/>
       <c r="F33" s="31" t="n"/>
@@ -1057,7 +1081,7 @@
       </c>
       <c r="C34" s="29" t="n"/>
       <c r="D34" s="30" t="n">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="E34" s="31" t="n"/>
       <c r="F34" s="31" t="n"/>
@@ -1076,7 +1100,7 @@
       </c>
       <c r="C35" s="29" t="n"/>
       <c r="D35" s="30" t="n">
-        <v>280.505</v>
+        <v>314</v>
       </c>
       <c r="E35" s="31" t="n"/>
       <c r="F35" s="31" t="n"/>
@@ -1095,7 +1119,7 @@
       </c>
       <c r="C36" s="27" t="n"/>
       <c r="D36" s="30" t="n">
-        <v>342.12</v>
+        <v>382</v>
       </c>
       <c r="E36" s="31" t="n"/>
       <c r="F36" s="31" t="n"/>
@@ -1107,6 +1131,7 @@
       <c r="C37" s="14" t="n"/>
       <c r="D37" s="14" t="n"/>
     </row>
+    <row r="38"/>
     <row r="39" ht="19.5" customHeight="1" s="1">
       <c r="A39" s="13" t="inlineStr">
         <is>
@@ -1114,12 +1139,15 @@
         </is>
       </c>
     </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" s="9" t="n"/>
     </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" s="10" t="n"/>
     </row>
+    <row r="44"/>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
@@ -1129,15 +1157,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B32:C32"/>
     <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B35:C35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/BISAGRAS FICHAS HERRERO DISMAY.xlsx
+++ b/LISTAS/ma/BISAGRAS FICHAS HERRERO DISMAY.xlsx
@@ -958,14 +958,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="23" t="n">
-        <v>45233.58662822087</v>
+        <v>45286</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -1011,26 +1007,6 @@
       </c>
       <c r="E11" s="7" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
     <row r="32" ht="18" customHeight="1" s="1">
       <c r="A32" s="11" t="inlineStr">
         <is>
@@ -1062,7 +1038,7 @@
       </c>
       <c r="C33" s="29" t="n"/>
       <c r="D33" s="30" t="n">
-        <v>256</v>
+        <v>229.273</v>
       </c>
       <c r="E33" s="31" t="n"/>
       <c r="F33" s="31" t="n"/>
@@ -1081,7 +1057,7 @@
       </c>
       <c r="C34" s="29" t="n"/>
       <c r="D34" s="30" t="n">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="E34" s="31" t="n"/>
       <c r="F34" s="31" t="n"/>
@@ -1100,7 +1076,7 @@
       </c>
       <c r="C35" s="29" t="n"/>
       <c r="D35" s="30" t="n">
-        <v>314</v>
+        <v>280.505</v>
       </c>
       <c r="E35" s="31" t="n"/>
       <c r="F35" s="31" t="n"/>
@@ -1119,7 +1095,7 @@
       </c>
       <c r="C36" s="27" t="n"/>
       <c r="D36" s="30" t="n">
-        <v>382</v>
+        <v>342.12</v>
       </c>
       <c r="E36" s="31" t="n"/>
       <c r="F36" s="31" t="n"/>
@@ -1131,7 +1107,6 @@
       <c r="C37" s="14" t="n"/>
       <c r="D37" s="14" t="n"/>
     </row>
-    <row r="38"/>
     <row r="39" ht="19.5" customHeight="1" s="1">
       <c r="A39" s="13" t="inlineStr">
         <is>
@@ -1139,15 +1114,12 @@
         </is>
       </c>
     </row>
-    <row r="40"/>
     <row r="41">
       <c r="A41" s="9" t="n"/>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="A43" s="10" t="n"/>
     </row>
-    <row r="44"/>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
@@ -1157,15 +1129,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A1:D1"/>
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="B34:C34"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A1:D1"/>
     <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B36:C36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
